--- a/www/download/IND.capital_depreciation.s.us.rpA2.xlsx
+++ b/www/download/IND.capital_depreciation.s.us.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74031.509210943</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79198.3107193253</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85099.8371356917</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75727.8216919794</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81729.8547073177</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81314.1176749028</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73193.7582518738</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76607.355863452</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90572.4282288111</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106576.139143213</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117410.901612856</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121206.247196359</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139013.420886207</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156046.444909782</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153811.901354841</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,67 +775,67 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59901.0426002679</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58955.8214361285</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52871.3513691017</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53578.2391026702</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51904.1190995353</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46592.9164193703</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46102.1829849342</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48568.3359570759</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58379.2194962324</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65964.509659506</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67187.6205118588</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69340.3607585595</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76483.747158246</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -847,7 +852,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62182.6622563998</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61459.7852163008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54898.5796373611</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57959.8632996363</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58927.178840252</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54204.1396966795</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56140.9223292916</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59000.2544874741</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73014.0204700645</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85672.9263729353</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90857.4369084485</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96451.1149533829</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109746.04455259</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124144.43780264</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119286.866911306</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3447.72564488812</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4056.45139437598</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3529.51632179635</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3363.56304269644</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3536.89036522245</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3192.59913736407</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3620.46079664702</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4158.10523720059</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5161.27485912345</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5890.67711845049</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6688.3511466785</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8068.78907233715</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9931.60253167939</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12849.9641821979</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11756.8761003702</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176456.739795647</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171881.591541854</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171384.406107029</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160891.712033725</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113760.958790005</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131607.250077569</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118662.525337633</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112217.792776431</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120483.288061918</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141621.64922617</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179120.441546385</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204740.203811757</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252043.150529306</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314590.733405019</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296158.785803693</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110870.363944736</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117244.46371809</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127007.36102905</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130067.787332087</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>144686.094520039</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158998.256033625</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158423.652491121</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161117.57311878</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190360.944477713</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219271.2613444</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249238.733171195</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>284574.204390954</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>332123.988034219</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>364655.895246358</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>345954.770618337</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163378.655003885</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183162.448359724</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199677.709420039</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209338.047707817</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>224450.104161822</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236929.883457422</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254904.737392344</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276202.458993369</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>310251.676613023</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>359236.661215187</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403939.598095065</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451986.393598311</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>505209.208239686</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>645691.061096243</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>646229.815485878</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,72 +1297,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1801.60642508965</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1885.24202254569</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1842.95376845835</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1995.49941526408</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1973.87655566176</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1885.15426599401</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1902.78882302786</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2218.23423176032</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2577.0655686432</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2939.68158238706</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2989.28895231551</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3334.34051158918</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3862.56328610428</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4674.07128540555</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1369,7 +1374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,67 +1384,67 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19360.2057226818</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21521.4520795566</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19706.0384506856</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20615.0327547192</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19640.284233541</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18330.6763545838</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18993.3372687644</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21957.7937929188</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25196.3356097143</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28711.2889260767</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30459.2137315567</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32751.7996633133</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37621.2700643706</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1456,7 +1461,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,67 +1471,67 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545091.443710321</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>534115.768423765</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>481628.808970487</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487508.218568299</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>475748.678829375</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>431506.788696572</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>420795.060472542</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446076.710621606</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>524492.793947102</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>585167.597490354</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>584756.219184891</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>591668.458139547</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>669238.552231181</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1543,7 +1548,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,67 +1558,67 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43861.1988105663</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42639.5074734847</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37539.4074308078</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37095.3679527012</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36258.1552354508</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32077.3538309134</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31029.8023038557</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32682.0896666281</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38628.7880709085</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43816.496792744</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43196.1392134982</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44064.2666732117</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49859.7500613318</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1630,7 +1635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,67 +1645,67 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111897.430452834</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117807.171481491</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108524.751577177</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111980.262251848</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114414.474727125</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111181.561355402</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113379.834332325</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126635.044450346</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163392.96590868</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>193063.439321445</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207955.822676289</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226159.555082345</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267551.938753399</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1717,7 +1722,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>967.099672186975</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1096.7654687633</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1131.4188948865</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1154.97389298963</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1224.4171558303</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1215.66951007819</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1571.23836316282</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1519.36704465963</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2041.95741456902</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2529.5653232159</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2515.11453711442</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3133.10485768548</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3917.59063730745</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4279.21714478719</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3781.46945619082</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,67 +1819,67 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29434.7894310522</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26365.5260503027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24099.328130321</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23518.8618626669</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22374.8318174798</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20485.1236655733</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21545.0830131354</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22378.5344811173</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26699.28266116</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29702.3915195364</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30476.6065741515</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31487.5915397625</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35722.9024123712</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1891,7 +1896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,67 +1906,67 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368936.495761504</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374764.48329163</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335780.252283257</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341390.915017351</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336675.801301864</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304371.927123232</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304156.833678665</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>325909.107965684</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391806.062005809</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>446675.660307622</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467880.918878405</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>495782.294355566</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568435.887594481</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1978,7 +1983,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,67 +1993,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212500.162011772</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>224602.795790781</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237166.043027899</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253307.032621812</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252781.185252721</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239970.98559699</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221271.799996857</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228901.138099981</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249466.205245908</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>297167.948036634</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300280.684492764</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303938.098384946</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>358119.468280028</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2065,7 +2070,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23188.1171342923</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25900.4379928804</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25440.6005235069</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26326.9602209037</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28279.773219909</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26109.0195990388</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26244.8068278759</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32235.9102570489</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40148.5025167437</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48118.0436104442</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50696.7558147196</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52673.3696423062</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64730.9968994728</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79534.767314545</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77802.7010297477</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,67 +2167,67 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24304.5814167978</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23651.167794313</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21725.0215732598</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20648.6634398311</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20052.6737212134</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17200.1115339258</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17030.5062153724</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19352.8263208026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23410.4365570017</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27383.1279901209</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28516.1745862453</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28261.7747013932</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33488.6332777695</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2239,7 +2244,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48825.329334992</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53890.5594980207</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51037.0041872361</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26742.7088390645</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31284.4814312497</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33934.4750191497</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33025.3248152127</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37162.4702735546</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41722.9342117947</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49851.9702950525</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51938.7931268496</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67691.0060264783</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80102.8851228427</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97543.8631333117</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97844.1351524629</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79659.7714734204</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81953.3621818118</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83116.05102857</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79258.8713993947</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86424.6759602973</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91264.8480153773</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97869.6705282442</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102907.829816439</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120416.277661068</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138799.355526106</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166184.524876129</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191436.933187129</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247279.834367286</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268488.565290632</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>276598.975512559</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,67 +2428,67 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10514.200186931</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11044.4194937954</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11151.7031242688</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11305.0612827041</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11683.5268741575</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10878.212509104</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10639.0917351734</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11655.9578944585</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14520.3084097658</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16623.8437844044</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18821.696288396</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21012.9477639421</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27072.505507697</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2500,7 +2505,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,67 +2515,67 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>533987.2251955</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>585797.963056151</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553845.317462387</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>560042.866636669</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>544779.997723464</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>490862.299620708</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487753.870096426</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>535445.917174024</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>650426.752640543</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>733498.959257805</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>753665.752208157</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>784118.463098888</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>894269.069094088</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2587,7 +2592,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1238577.27673467</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>1135587.3850905</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1055483.71619686</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>992382.890236023</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1182799.27149798</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1310499.49508807</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1202462.87013806</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1148355.30447645</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>1255511.94484904</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1361019.55503367</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1386771.57974616</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1361629.24965676</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1401105.22131454</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1684818.85989241</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>1822179.78509325</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145883.213984109</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158021.42916051</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150136.590747949</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108933.929406134</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133260.804699939</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152461.199303685</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136306.255719661</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150949.507231172</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166236.839270636</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179758.671079501</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>208079.568811872</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234989.61719292</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255150.264156843</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247664.328440945</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222593.277422626</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1392.3987857604</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1577.94541662314</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1859.27887218759</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1957.24631743657</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1970.09256789277</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2092.75656972439</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2353.13364660797</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2649.18477311275</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3237.88281306627</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3838.67502997525</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4438.3889803169</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5125.08748123012</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6478.83406944057</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7785.76745287189</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7146.10989932949</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4175.97367807492</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4262.33057798998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4201.89573519058</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4246.50582703679</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4606.21276887394</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4194.69825802974</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4462.05534599035</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4764.50443846394</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5605.69135876413</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6783.45067121095</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7486.53790454033</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7733.91176882276</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9099.78319780626</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10311.1196757243</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9249.29863451588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1121.04857534057</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1444.31150787025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1548.1476282494</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1637.76013295514</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1780.26888633514</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1952.37820152961</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2012.9015483561</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2023.94165044062</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2328.8331605944</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2717.19442423764</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3191.49660903645</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4062.03131246715</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6012.11142013061</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7247.18925429016</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6335.51879334942</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76247.8401745717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88208.677267923</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105366.54201057</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116903.423250568</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127825.26007938</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145785.517408533</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149723.19221145</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141915.765422544</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131634.291310728</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139101.288198527</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151623.754821279</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162996.298566998</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171964.046082496</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185388.454974458</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166532.865973396</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>935.033766716748</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>962.436088886035</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>878.112097574302</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>988.361789538299</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1028.45972006696</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1079.4579623307</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>862.927322251072</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>857.643554506389</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1092.12927592513</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1192.83169298121</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1235.83258064407</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1428.20462482944</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1649.43198151582</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1868.92749049352</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1817.72581885165</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,67 +3211,67 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110051.613121773</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108526.400879063</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97134.9665358162</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98288.8959109143</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96451.8829182127</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85897.808974582</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81554.2305194016</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83885.6830009321</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103258.202894404</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113762.028194282</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113955.845160289</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119046.714460891</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131248.655510072</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3283,7 +3288,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,67 +3298,67 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32576.0339670849</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36808.2738750884</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39096.1452575262</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42666.8431366874</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43137.6454940369</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44093.3977422624</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46807.1881066426</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49867.4481896885</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55784.322017333</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63773.1867390281</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72651.060032066</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78521.8156547962</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95388.6672297573</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3370,7 +3375,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,72 +3385,72 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17731.4246456308</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18615.5934765216</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17439.6391239375</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18170.0777138217</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18623.7065760445</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18155.4086054125</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18466.7562704419</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20533.3261419113</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25315.7365269341</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28985.3787072453</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30153.6234109167</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34436.3887548414</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40460.3207052331</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55530.5518496543</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3457,7 +3462,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8621.88665148551</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9226.6580996365</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9071.52692359665</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10080.3634535941</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8992.88718455405</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9722.7172574683</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10712.9624327706</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12003.1931111439</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15137.8121786785</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18726.5610163955</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23707.9999548669</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29239.72564936</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39551.4044013844</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46167.2743920515</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39101.4384900643</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60322.0338121859</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79310.3707332916</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80742.2991077465</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73431.3567097784</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38895.9306411891</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51416.9833576182</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59016.8468249524</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64307.2620314196</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76553.8288102808</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99432.3443358154</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119651.786736151</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145357.078662039</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194949.386282253</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251866.957028499</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226246.802231757</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4836.19096461471</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5701.62837290588</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6135.64293581954</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6877.212381587</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6487.1615341003</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5674.46111006042</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6827.95496708534</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7746.74847322426</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9881.98885097931</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11642.6934697896</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13410.6979202162</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14373.2192606829</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18748.8787394605</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22017.7754302872</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20919.2346228943</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4600.07350075678</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4509.21042852256</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4316.10353506834</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4747.61153442491</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4803.44439850744</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4146.60082110677</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4191.53133922894</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4462.08020053235</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5586.82484942675</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6778.10119338425</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7120.80529720394</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7703.03613571858</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8850.07892662694</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10928.0606762985</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7715.81201843587</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,67 +3820,67 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48664.0245698599</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53484.099109837</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50572.9831406212</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52046.5431885725</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54864.259842949</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53432.1445377011</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48358.4082237311</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52006.600409208</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62542.9067994847</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64230.6436042982</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65520.3671164255</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67553.0926450966</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77102.2193546365</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3892,7 +3897,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50285.1103942363</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54077.1270264984</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57121.9452990314</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60402.6002907757</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55702.0597379603</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60834.3176809768</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47348.8132081669</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48630.5337446611</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59459.8785830553</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77499.3092627744</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89080.2997914161</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100673.708935067</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114371.299749517</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141163.370602808</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119057.988207421</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37840.9451226263</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39172.5425932418</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42526.5860996838</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43035.5940772088</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49723.1898636696</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58566.5527948832</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53069.9843390756</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52521.9195117726</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55437.0219881852</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63853.6183875367</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66840.5141894893</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67763.8504520565</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73131.7358711163</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80320.2970282769</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76776.1213821351</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1399827.26803539</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1443082.12201214</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1499854.86951382</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1523889.99594355</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1607511.00123559</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1706741.1994334</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1747700.9362169</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>1735706.62610792</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1752771.61836829</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1815309.71499575</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1899793.23249477</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1999850.73103332</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>2111579.01048659</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>2255094.07155205</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.308</t>
+          <t>2307970.69815729</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>834359.584527764</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>875995.799515621</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>888232.735690991</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>817887.455920437</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>820870.645971099</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>836667.08690153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>817433.866052652</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>808667.728954467</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>900867.030276919</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1020802.53907012</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1174139.92751623</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>1288849.39089663</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1462975.42687985</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1414733.6337512</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1300131.74826274</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6.783</t>
+          <t>6782647.33020936</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>6921569.83571776</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6799923.18790552</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6.672</t>
+          <t>6672392.99758787</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>6921926.22014192</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7.098</t>
+          <t>7097527.55120248</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6.958</t>
+          <t>6957930.10248792</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7.077</t>
+          <t>7076765.80994838</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7.851</t>
+          <t>7851414.30481901</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8.707</t>
+          <t>8707490.97895034</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9.294</t>
+          <t>9293630.10720785</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>9.845</t>
+          <t>9845214.4705543</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>10.986</t>
+          <t>10985641.7858809</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8.495</t>
+          <t>8495405.66030324</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8.363</t>
+          <t>8363000.72243344</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>capital_depreciation.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
